--- a/data/batches/B13_TrialSummary_TS_part1/Test_Validation_Report/Test_Validation_Report_B13.xlsx
+++ b/data/batches/B13_TrialSummary_TS_part1/Test_Validation_Report/Test_Validation_Report_B13.xlsx
@@ -2129,11 +2129,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2208,11 +2204,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2287,11 +2279,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2366,11 +2354,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2445,11 +2429,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2524,11 +2504,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2603,11 +2579,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2682,11 +2654,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2761,11 +2729,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2840,11 +2804,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>TSPARMCD</t>
@@ -2919,11 +2879,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>TSVALCD</t>
@@ -2950,11 +2906,7 @@
           <t>INCONSISTENT VALUE</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>C49487</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -2977,7 +2929,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -3002,11 +2954,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>TSVALCD</t>
@@ -3029,11 +2977,7 @@
           <t>INCONSISTENT VALUE</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>C49487</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>No</t>
@@ -3056,7 +3000,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -3081,11 +3025,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>TSVALCD</t>
@@ -3108,11 +3048,7 @@
           <t>INCONSISTENT VALUE</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>C49487</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>No</t>
@@ -3135,7 +3071,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -3160,11 +3096,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>TSVALCD</t>
@@ -3187,11 +3119,7 @@
           <t>INCONSISTENT VALUE</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>C82640</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>No</t>
@@ -3214,7 +3142,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -3239,11 +3167,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>TSVALCD</t>
@@ -3270,11 +3194,7 @@
           <t>INCONSISTENT VALUE</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>C1909</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>No</t>
@@ -3297,7 +3217,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -3322,11 +3242,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>TSVALCD</t>
@@ -3349,11 +3265,7 @@
           <t>INCONSISTENT VALUE</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>C49487</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>No</t>
@@ -3376,7 +3288,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -3401,11 +3313,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>TSVALCD</t>
@@ -3428,11 +3336,7 @@
           <t>INCONSISTENT VALUE</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>C49487</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>No</t>
@@ -3455,7 +3359,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -3480,11 +3384,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>TSVALCD</t>
@@ -3511,11 +3411,7 @@
           <t>INCONSISTENT VALUE</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>C49487</t>
-        </is>
-      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3538,7 +3434,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -3563,11 +3459,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>TSVALCD</t>
@@ -3590,11 +3482,7 @@
           <t>INCONSISTENT VALUE</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>C49487</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>No</t>
@@ -3617,7 +3505,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -3642,11 +3530,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>TSVALCD</t>
@@ -3669,11 +3553,7 @@
           <t>INCONSISTENT VALUE</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>C49487</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>No</t>
@@ -3696,7 +3576,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -3721,11 +3601,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>TSVALCD</t>
@@ -3748,11 +3624,7 @@
           <t>INCONSISTENT VALUE</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>C98388</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>No</t>
@@ -3775,7 +3647,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -3800,11 +3672,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>TSVALCD</t>
@@ -3827,11 +3695,7 @@
           <t>INCONSISTENT VALUE</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>C49656</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>No</t>
@@ -3854,7 +3718,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -3879,11 +3743,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>TSVALCD</t>
@@ -3906,11 +3766,7 @@
           <t>INCONSISTENT VALUE</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>C15601</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>No</t>
@@ -3933,7 +3789,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -3958,11 +3814,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>TSVALCD</t>
@@ -3985,11 +3837,7 @@
           <t>INCONSISTENT VALUE</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>C49666</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>No</t>
@@ -4012,7 +3860,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -4037,11 +3885,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -4112,11 +3956,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -4183,11 +4023,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -4254,11 +4090,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -4325,11 +4157,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -4400,11 +4228,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -4475,11 +4299,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -4550,11 +4370,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -4621,11 +4437,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -4692,11 +4504,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -4763,11 +4571,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -4838,11 +4642,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -4909,11 +4709,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -4984,11 +4780,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -5055,11 +4847,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -5126,11 +4914,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -5197,11 +4981,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -5268,11 +5048,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -5339,11 +5115,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -5410,11 +5182,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -5485,11 +5253,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -5560,11 +5324,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -5631,11 +5391,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -5706,11 +5462,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -5777,11 +5529,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -5852,11 +5600,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -5923,11 +5667,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -5998,11 +5738,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -6073,11 +5809,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -6148,11 +5880,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -6205,11 +5933,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -6262,11 +5986,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -6319,11 +6039,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>TSVCDREF</t>
@@ -6376,26 +6092,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
       <c r="H59" t="n">
         <v>2</v>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 2; count=1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 2; count=1</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr">
         <is>
           <t>No</t>
@@ -6408,7 +6146,7 @@
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -6433,26 +6171,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
       <c r="H60" t="n">
         <v>3</v>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 3; count=1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 3; count=0</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr">
         <is>
           <t>No</t>
@@ -6465,7 +6225,7 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -6490,26 +6250,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>2</v>
+      </c>
       <c r="H61" t="n">
         <v>4</v>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 4; count=1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 4; count=0</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr">
         <is>
           <t>No</t>
@@ -6522,7 +6304,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -6547,26 +6329,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>3</v>
+      </c>
       <c r="H62" t="n">
         <v>5</v>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 5; count=1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 5; count=0</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr">
         <is>
           <t>No</t>
@@ -6579,7 +6383,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -6604,26 +6408,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>4</v>
+      </c>
       <c r="H63" t="n">
         <v>6</v>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 6; count=1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 6; count=0</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr">
         <is>
           <t>No</t>
@@ -6636,7 +6462,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -6661,26 +6487,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>5</v>
+      </c>
       <c r="H64" t="n">
         <v>7</v>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 7; count=1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 7; count=0</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
           <t>No</t>
@@ -6693,7 +6541,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -6718,26 +6566,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="n">
+        <v>6</v>
+      </c>
       <c r="H65" t="n">
         <v>8</v>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 8; count=1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 8; count=0</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>No</t>
@@ -6750,7 +6620,7 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -6775,26 +6645,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>7</v>
+      </c>
       <c r="H66" t="n">
         <v>9</v>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 9; count=1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 9; count=0</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr">
         <is>
           <t>No</t>
@@ -6807,7 +6699,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -6832,26 +6724,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>8</v>
+      </c>
       <c r="H67" t="n">
         <v>10</v>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 10; count=1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 10; count=0</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr">
         <is>
           <t>No</t>
@@ -6864,7 +6778,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -6889,26 +6803,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>9</v>
+      </c>
       <c r="H68" t="n">
         <v>11</v>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 11; count=1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 11; count=0</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr">
         <is>
           <t>No</t>
@@ -6921,7 +6857,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -6946,26 +6882,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>10</v>
+      </c>
       <c r="H69" t="n">
         <v>12</v>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 12; count=1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 12; count=0</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
           <t>No</t>
@@ -6978,7 +6936,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7003,26 +6961,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>11</v>
+      </c>
       <c r="H70" t="n">
         <v>13</v>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 13; count=1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 13; count=0</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr">
         <is>
           <t>No</t>
@@ -7035,7 +7015,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7060,26 +7040,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>12</v>
+      </c>
       <c r="H71" t="n">
         <v>14</v>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 14; count=1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 14; count=0</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr">
         <is>
           <t>No</t>
@@ -7092,7 +7094,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7117,26 +7119,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>13</v>
+      </c>
       <c r="H72" t="n">
         <v>15</v>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 15; count=1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 15; count=0</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr">
         <is>
           <t>No</t>
@@ -7149,7 +7173,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7174,26 +7198,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="n">
+        <v>14</v>
+      </c>
       <c r="H73" t="n">
         <v>16</v>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 16; count=1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 16; count=1</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr">
         <is>
           <t>No</t>
@@ -7206,7 +7252,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7231,26 +7277,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="n">
+        <v>15</v>
+      </c>
       <c r="H74" t="n">
         <v>17</v>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 17; count=1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 17; count=1</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr">
         <is>
           <t>No</t>
@@ -7263,7 +7331,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7288,26 +7356,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="n">
+        <v>16</v>
+      </c>
       <c r="H75" t="n">
         <v>18</v>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 18; count=1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 18; count=1</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr">
         <is>
           <t>No</t>
@@ -7320,7 +7410,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7345,26 +7435,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>17</v>
+      </c>
       <c r="H76" t="n">
         <v>19</v>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 19; count=1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 19; count=1</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr">
         <is>
           <t>No</t>
@@ -7377,7 +7489,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7402,26 +7514,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="n">
+        <v>18</v>
+      </c>
       <c r="H77" t="n">
         <v>20</v>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 20; count=1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 20; count=0</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr">
         <is>
           <t>No</t>
@@ -7434,7 +7568,7 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7459,26 +7593,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="n">
+        <v>19</v>
+      </c>
       <c r="H78" t="n">
         <v>21</v>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 21; count=1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 21; count=1</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr">
         <is>
           <t>No</t>
@@ -7491,7 +7647,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7516,26 +7672,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>20</v>
+      </c>
       <c r="H79" t="n">
         <v>22</v>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 22; count=1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 22; count=0</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr">
         <is>
           <t>No</t>
@@ -7548,7 +7726,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7573,26 +7751,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="n">
+        <v>21</v>
+      </c>
       <c r="H80" t="n">
         <v>23</v>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 23; count=1</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 23; count=0</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O80" t="inlineStr">
         <is>
           <t>No</t>
@@ -7605,7 +7805,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7630,26 +7830,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="n">
+        <v>22</v>
+      </c>
       <c r="H81" t="n">
         <v>24</v>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 24; count=1</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 24; count=0</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>No</t>
@@ -7662,7 +7884,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7687,26 +7909,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>23</v>
+      </c>
       <c r="H82" t="n">
         <v>25</v>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 25; count=1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 25; count=0</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O82" t="inlineStr">
         <is>
           <t>No</t>
@@ -7719,7 +7963,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7744,26 +7988,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="n">
+        <v>24</v>
+      </c>
       <c r="H83" t="n">
         <v>26</v>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 26; count=1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 26; count=0</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O83" t="inlineStr">
         <is>
           <t>No</t>
@@ -7776,7 +8042,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7801,26 +8067,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="n">
+        <v>25</v>
+      </c>
       <c r="H84" t="n">
         <v>27</v>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 27; count=1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 27; count=0</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O84" t="inlineStr">
         <is>
           <t>No</t>
@@ -7833,7 +8121,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7858,26 +8146,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="n">
+        <v>26</v>
+      </c>
       <c r="H85" t="n">
         <v>28</v>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 28; count=1</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 28; count=0</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O85" t="inlineStr">
         <is>
           <t>No</t>
@@ -7890,7 +8200,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7915,26 +8225,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="n">
+        <v>27</v>
+      </c>
       <c r="H86" t="n">
         <v>29</v>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 29; count=1</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 29; count=1</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O86" t="inlineStr">
         <is>
           <t>No</t>
@@ -7947,7 +8279,7 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -7972,26 +8304,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="n">
+        <v>28</v>
+      </c>
       <c r="H87" t="n">
         <v>30</v>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 30; count=1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 30; count=0</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O87" t="inlineStr">
         <is>
           <t>No</t>
@@ -8004,7 +8358,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8029,26 +8383,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="n">
+        <v>29</v>
+      </c>
       <c r="H88" t="n">
         <v>31</v>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 31; count=1</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 31; count=1</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O88" t="inlineStr">
         <is>
           <t>No</t>
@@ -8061,7 +8437,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8086,26 +8462,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="n">
+        <v>30</v>
+      </c>
       <c r="H89" t="n">
         <v>32</v>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 32; count=1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 32; count=0</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O89" t="inlineStr">
         <is>
           <t>No</t>
@@ -8118,7 +8516,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8143,26 +8541,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="n">
+        <v>31</v>
+      </c>
       <c r="H90" t="n">
         <v>33</v>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 33; count=1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 33; count=0</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O90" t="inlineStr">
         <is>
           <t>No</t>
@@ -8175,7 +8595,7 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8200,26 +8620,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="n">
+        <v>32</v>
+      </c>
       <c r="H91" t="n">
         <v>34</v>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 34; count=1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 34; count=0</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O91" t="inlineStr">
         <is>
           <t>No</t>
@@ -8232,7 +8674,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8257,26 +8699,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="n">
+        <v>33</v>
+      </c>
       <c r="H92" t="n">
         <v>35</v>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 35; count=1</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 35; count=1</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O92" t="inlineStr">
         <is>
           <t>No</t>
@@ -8289,7 +8753,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8314,26 +8778,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="n">
+        <v>34</v>
+      </c>
       <c r="H93" t="n">
         <v>36</v>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 36; count=1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 36; count=0</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O93" t="inlineStr">
         <is>
           <t>No</t>
@@ -8346,7 +8832,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8371,26 +8857,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="n">
+        <v>35</v>
+      </c>
       <c r="H94" t="n">
         <v>37</v>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 37; count=1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 37; count=0</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O94" t="inlineStr">
         <is>
           <t>No</t>
@@ -8403,7 +8911,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8428,26 +8936,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="n">
+        <v>36</v>
+      </c>
       <c r="H95" t="n">
         <v>38</v>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 38; count=1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 38; count=0</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O95" t="inlineStr">
         <is>
           <t>No</t>
@@ -8460,7 +8990,7 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8485,26 +9015,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="n">
+        <v>37</v>
+      </c>
       <c r="H96" t="n">
         <v>39</v>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 39; count=1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 39; count=0</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O96" t="inlineStr">
         <is>
           <t>No</t>
@@ -8517,7 +9069,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8542,26 +9094,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="n">
+        <v>38</v>
+      </c>
       <c r="H97" t="n">
         <v>40</v>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 40; count=1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 40; count=0</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O97" t="inlineStr">
         <is>
           <t>No</t>
@@ -8574,7 +9148,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8599,39 +9173,61 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="n">
+        <v>39</v>
+      </c>
       <c r="H98" t="n">
         <v>41</v>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 41; count=1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 41; count=2</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -8656,26 +9252,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="n">
+        <v>40</v>
+      </c>
       <c r="H99" t="n">
         <v>42</v>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 42; count=1</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 42; count=0</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O99" t="inlineStr">
         <is>
           <t>No</t>
@@ -8688,7 +9306,7 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8713,26 +9331,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="n">
+        <v>41</v>
+      </c>
       <c r="H100" t="n">
         <v>43</v>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 43; count=1</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 43; count=0</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O100" t="inlineStr">
         <is>
           <t>No</t>
@@ -8745,7 +9385,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8770,26 +9410,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="n">
+        <v>42</v>
+      </c>
       <c r="H101" t="n">
         <v>44</v>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 44; count=1</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 44; count=0</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O101" t="inlineStr">
         <is>
           <t>No</t>
@@ -8802,7 +9464,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8827,26 +9489,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="n">
+        <v>43</v>
+      </c>
       <c r="H102" t="n">
         <v>45</v>
       </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 45; count=1</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 45; count=0</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O102" t="inlineStr">
         <is>
           <t>No</t>
@@ -8859,7 +9543,7 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8884,26 +9568,48 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
           <t>__row__</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
+      <c r="G103" t="n">
+        <v>44</v>
+      </c>
       <c r="H103" t="n">
         <v>46</v>
       </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 46; count=1</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>duplicated</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Complete Row @ CSV Row 46; count=0</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="O103" t="inlineStr">
         <is>
           <t>No</t>
@@ -8916,7 +9622,7 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Duplicate row injection mismatch</t>
         </is>
       </c>
     </row>
@@ -8941,11 +9647,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
           <t>__row__</t>
@@ -8973,7 +9675,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Row index 45 is out of bounds (Original TS.csv has 45 rows)</t>
         </is>
       </c>
     </row>
@@ -8998,11 +9700,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
           <t>__row__</t>
@@ -9030,7 +9728,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Row index 46 is out of bounds (Original TS.csv has 45 rows)</t>
         </is>
       </c>
     </row>
@@ -9055,11 +9753,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>__row__</t>
@@ -9087,7 +9781,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Row index 47 is out of bounds (Original TS.csv has 45 rows)</t>
         </is>
       </c>
     </row>
@@ -9112,11 +9806,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
           <t>__row__</t>
@@ -9144,7 +9834,7 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>USUBJID column missing for duplicate row validation</t>
+          <t>Row index 48 is out of bounds (Original TS.csv has 45 rows)</t>
         </is>
       </c>
     </row>
@@ -9169,11 +9859,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -9226,11 +9912,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -9283,11 +9965,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -9366,11 +10044,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -9449,11 +10123,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -9506,11 +10176,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -9563,11 +10229,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -9620,11 +10282,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -9677,11 +10335,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -9760,11 +10414,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -9843,11 +10493,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -9926,11 +10572,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -9983,11 +10625,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -10040,11 +10678,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -10123,11 +10757,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -10180,11 +10810,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -10263,11 +10889,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -10346,11 +10968,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -10403,11 +11021,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -10486,11 +11100,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -10543,11 +11153,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -10600,11 +11206,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -10657,11 +11259,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -10740,11 +11338,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -10823,11 +11417,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -10880,11 +11470,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -10937,11 +11523,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11020,11 +11602,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11103,11 +11681,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11160,11 +11734,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11217,11 +11787,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11274,11 +11840,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11357,11 +11919,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11440,11 +11998,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11523,11 +12077,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11580,11 +12130,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11637,11 +12183,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11694,11 +12236,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11751,11 +12289,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11808,11 +12342,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11865,11 +12395,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -11948,11 +12474,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -12031,11 +12553,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -12088,11 +12606,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -12145,11 +12659,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -12228,11 +12738,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -12311,11 +12817,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -12394,11 +12896,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -12477,11 +12975,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -12560,11 +13054,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr">
         <is>
           <t>TSVAL</t>
@@ -12617,11 +13107,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -12674,11 +13160,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -12749,11 +13231,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -12824,11 +13302,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -12881,11 +13355,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -12938,11 +13408,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -12995,11 +13461,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13070,11 +13532,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E165" t="inlineStr"/>
       <c r="F165" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13127,11 +13585,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13184,11 +13638,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E167" t="inlineStr"/>
       <c r="F167" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13259,11 +13709,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13316,11 +13762,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E169" t="inlineStr"/>
       <c r="F169" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13391,11 +13833,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr"/>
       <c r="F170" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13466,11 +13904,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13523,11 +13957,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13580,11 +14010,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E173" t="inlineStr"/>
       <c r="F173" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13655,11 +14081,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13730,11 +14152,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13787,11 +14205,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13844,11 +14258,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13901,11 +14311,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -13958,11 +14364,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14015,11 +14417,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14090,11 +14488,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14165,11 +14559,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14240,11 +14630,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14315,11 +14701,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14390,11 +14772,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14447,11 +14825,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14504,11 +14878,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14579,11 +14949,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14636,11 +15002,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14711,11 +15073,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14768,11 +15126,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14825,11 +15179,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14882,11 +15232,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -14957,11 +15303,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -15032,11 +15374,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -15089,11 +15427,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -15146,11 +15480,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -15203,11 +15533,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -15278,11 +15604,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E199" t="inlineStr"/>
       <c r="F199" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -15335,11 +15657,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -15410,11 +15728,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -15485,11 +15799,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -15542,11 +15852,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -15617,11 +15923,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -15674,11 +15976,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -15749,11 +16047,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
           <t>TSVALNF</t>
@@ -15806,11 +16100,7 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
         <is>
           <t>TSVALNF</t>
